--- a/grupos/1AM - Estadisticos 20241.xlsx
+++ b/grupos/1AM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="113">
   <si>
     <t>Materia</t>
   </si>
@@ -230,18 +230,18 @@
     <t>Velasco Sánchez David</t>
   </si>
   <si>
+    <t>Faltante Faltante Faltante</t>
+  </si>
+  <si>
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
-  </si>
-  <si>
-    <t>Faltante Faltante Faltante</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -263,16 +263,31 @@
     <t>IXMATLAHUA</t>
   </si>
   <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>CUICAHUA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>MENCIAS</t>
   </si>
   <si>
-    <t>RUIZ</t>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
   </si>
   <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>VASQUEZ</t>
+    <t>TZITZIHUA</t>
   </si>
   <si>
     <t>JUAN</t>
@@ -284,16 +299,28 @@
     <t>CALIHUA</t>
   </si>
   <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>GIL</t>
+  </si>
+  <si>
+    <t>TINOCO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>JORGE</t>
   </si>
   <si>
-    <t>SANTOS</t>
+    <t>MUÑOZ</t>
   </si>
   <si>
     <t>TEZOCO</t>
   </si>
   <si>
-    <t>ROJAS</t>
+    <t>DE LA CRUZ</t>
   </si>
   <si>
     <t>GIOVANNI ARIEL</t>
@@ -305,16 +332,31 @@
     <t>JESUS ANTONIO</t>
   </si>
   <si>
+    <t>ALEXIS URIEL</t>
+  </si>
+  <si>
+    <t>PABLO AZAEL</t>
+  </si>
+  <si>
+    <t>ANGEL MOISES</t>
+  </si>
+  <si>
+    <t>JOY JARA</t>
+  </si>
+  <si>
     <t>JAVIER</t>
   </si>
   <si>
-    <t>ALEXIS URIEL</t>
+    <t>IAN</t>
+  </si>
+  <si>
+    <t>EDGAR</t>
   </si>
   <si>
     <t>OSMAR EDUARDO</t>
   </si>
   <si>
-    <t>ALDAIR</t>
+    <t>ELIZABETH</t>
   </si>
 </sst>
 </file>
@@ -860,28 +902,28 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K4">
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
         <v>-1</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -908,19 +950,19 @@
         <v>-1</v>
       </c>
       <c r="Z4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA4">
         <v>8</v>
       </c>
       <c r="AB4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC4">
         <v>8</v>
       </c>
       <c r="AD4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE4">
         <v>8</v>
@@ -961,28 +1003,28 @@
         <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K5">
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
         <v>-1</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -1015,13 +1057,13 @@
         <v>5</v>
       </c>
       <c r="AB5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC5">
         <v>5</v>
       </c>
       <c r="AD5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE5">
         <v>6</v>
@@ -1062,28 +1104,28 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
         <v>-1</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1122,7 +1164,7 @@
         <v>10</v>
       </c>
       <c r="AD6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE6">
         <v>9</v>
@@ -1163,28 +1205,28 @@
         <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O7">
         <v>-1</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1217,10 +1259,10 @@
         <v>6</v>
       </c>
       <c r="AB7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD7">
         <v>6</v>
@@ -1264,28 +1306,28 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O8">
         <v>-1</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1318,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="AB8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC8">
         <v>7</v>
@@ -1330,7 +1372,7 @@
         <v>10</v>
       </c>
       <c r="AF8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG8">
         <v>10</v>
@@ -1365,28 +1407,28 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K9">
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
         <v>-1</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1425,7 +1467,7 @@
         <v>10</v>
       </c>
       <c r="AD9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE9">
         <v>9</v>
@@ -1466,28 +1508,28 @@
         <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K10">
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O10">
         <v>-1</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1523,7 +1565,7 @@
         <v>5</v>
       </c>
       <c r="AC10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD10">
         <v>6</v>
@@ -1535,7 +1577,7 @@
         <v>5</v>
       </c>
       <c r="AG10">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:33">
@@ -1567,28 +1609,28 @@
         <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
         <v>-1</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1615,7 +1657,7 @@
         <v>-1</v>
       </c>
       <c r="Z11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA11">
         <v>5</v>
@@ -1633,10 +1675,10 @@
         <v>5</v>
       </c>
       <c r="AF11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG11">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:33">
@@ -1668,28 +1710,28 @@
         <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K12">
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
         <v>-1</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1725,7 +1767,7 @@
         <v>10</v>
       </c>
       <c r="AC12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD12">
         <v>8</v>
@@ -1734,7 +1776,7 @@
         <v>6</v>
       </c>
       <c r="AF12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG12">
         <v>10</v>
@@ -1769,28 +1811,28 @@
         <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
         <v>-1</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1826,10 +1868,10 @@
         <v>10</v>
       </c>
       <c r="AC13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE13">
         <v>10</v>
@@ -1870,28 +1912,28 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K14">
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
         <v>-1</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1918,7 +1960,7 @@
         <v>-1</v>
       </c>
       <c r="Z14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA14">
         <v>7</v>
@@ -1927,7 +1969,7 @@
         <v>10</v>
       </c>
       <c r="AC14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD14">
         <v>8</v>
@@ -1936,7 +1978,7 @@
         <v>7</v>
       </c>
       <c r="AF14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG14">
         <v>10</v>
@@ -1971,28 +2013,28 @@
         <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
         <v>-1</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -2025,22 +2067,22 @@
         <v>7</v>
       </c>
       <c r="AB15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC15">
         <v>6</v>
       </c>
       <c r="AD15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE15">
         <v>10</v>
       </c>
       <c r="AF15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG15">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:33">
@@ -2072,28 +2114,28 @@
         <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
         <v>-1</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -2173,28 +2215,28 @@
         <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
         <v>-1</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2221,16 +2263,16 @@
         <v>-1</v>
       </c>
       <c r="Z17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA17">
         <v>8</v>
       </c>
       <c r="AB17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD17">
         <v>7</v>
@@ -2239,7 +2281,7 @@
         <v>9</v>
       </c>
       <c r="AF17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG17">
         <v>10</v>
@@ -2274,28 +2316,28 @@
         <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K18">
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
         <v>-1</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2331,10 +2373,10 @@
         <v>6</v>
       </c>
       <c r="AC18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE18">
         <v>6</v>
@@ -2375,28 +2417,28 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
         <v>-1</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2435,7 +2477,7 @@
         <v>5</v>
       </c>
       <c r="AD19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE19">
         <v>5</v>
@@ -2476,28 +2518,28 @@
         <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K20">
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
         <v>-1</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2542,7 +2584,7 @@
         <v>10</v>
       </c>
       <c r="AF20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG20">
         <v>10</v>
@@ -2577,28 +2619,28 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K21">
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O21">
         <v>-1</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2625,25 +2667,25 @@
         <v>-1</v>
       </c>
       <c r="Z21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA21">
         <v>5</v>
       </c>
       <c r="AB21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC21">
         <v>5</v>
       </c>
       <c r="AD21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE21">
         <v>7</v>
       </c>
       <c r="AF21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG21">
         <v>10</v>
@@ -2678,28 +2720,28 @@
         <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K22">
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
         <v>-1</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2735,10 +2777,10 @@
         <v>10</v>
       </c>
       <c r="AC22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE22">
         <v>9</v>
@@ -2779,28 +2821,28 @@
         <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K23">
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
         <v>-1</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2827,7 +2869,7 @@
         <v>-1</v>
       </c>
       <c r="Z23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA23">
         <v>7</v>
@@ -2836,10 +2878,10 @@
         <v>9</v>
       </c>
       <c r="AC23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE23">
         <v>8</v>
@@ -2880,28 +2922,28 @@
         <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K24">
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
         <v>-1</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2928,7 +2970,7 @@
         <v>-1</v>
       </c>
       <c r="Z24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA24">
         <v>5</v>
@@ -2940,7 +2982,7 @@
         <v>5</v>
       </c>
       <c r="AD24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE24">
         <v>7</v>
@@ -2981,28 +3023,28 @@
         <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K25">
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O25">
         <v>-1</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -3038,10 +3080,10 @@
         <v>8</v>
       </c>
       <c r="AC25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE25">
         <v>8</v>
@@ -3082,28 +3124,28 @@
         <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K26">
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O26">
         <v>-1</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -3139,7 +3181,7 @@
         <v>9</v>
       </c>
       <c r="AC26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD26">
         <v>7</v>
@@ -3183,28 +3225,28 @@
         <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K27">
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
         <v>-1</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -3237,13 +3279,13 @@
         <v>5</v>
       </c>
       <c r="AB27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC27">
         <v>5</v>
       </c>
       <c r="AD27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE27">
         <v>7</v>
@@ -3284,28 +3326,28 @@
         <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K28">
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
         <v>-1</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -3341,16 +3383,16 @@
         <v>7</v>
       </c>
       <c r="AC28">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AD28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE28">
         <v>10</v>
       </c>
       <c r="AF28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG28">
         <v>10</v>
@@ -3385,28 +3427,28 @@
         <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O29">
         <v>-1</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -3433,16 +3475,16 @@
         <v>-1</v>
       </c>
       <c r="Z29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA29">
         <v>8</v>
       </c>
       <c r="AB29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD29">
         <v>7</v>
@@ -3486,28 +3528,28 @@
         <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K30">
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O30">
         <v>-1</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -3546,7 +3588,7 @@
         <v>5</v>
       </c>
       <c r="AD30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE30">
         <v>5</v>
@@ -3587,28 +3629,28 @@
         <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K31">
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O31">
         <v>-1</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -3635,28 +3677,28 @@
         <v>-1</v>
       </c>
       <c r="Z31">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA31">
         <v>6</v>
       </c>
       <c r="AB31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AC31">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AD31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE31">
         <v>6</v>
       </c>
       <c r="AF31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG31">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:33">
@@ -3688,28 +3730,28 @@
         <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K32">
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O32">
         <v>-1</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
         <v>-1</v>
@@ -3754,7 +3796,7 @@
         <v>9</v>
       </c>
       <c r="AF32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG32">
         <v>10</v>
@@ -3789,28 +3831,28 @@
         <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K33">
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O33">
         <v>-1</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>-1</v>
@@ -3837,7 +3879,7 @@
         <v>-1</v>
       </c>
       <c r="Z33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA33">
         <v>7</v>
@@ -3849,13 +3891,13 @@
         <v>10</v>
       </c>
       <c r="AD33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE33">
         <v>9</v>
       </c>
       <c r="AF33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG33">
         <v>10</v>
@@ -3890,28 +3932,28 @@
         <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K34">
         <v>-1</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O34">
         <v>-1</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>-1</v>
@@ -3938,19 +3980,19 @@
         <v>-1</v>
       </c>
       <c r="Z34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA34">
         <v>5</v>
       </c>
       <c r="AB34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE34">
         <v>9</v>
@@ -3991,28 +4033,28 @@
         <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K35">
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O35">
         <v>-1</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>-1</v>
@@ -4039,7 +4081,7 @@
         <v>-1</v>
       </c>
       <c r="Z35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA35">
         <v>7</v>
@@ -4051,13 +4093,13 @@
         <v>10</v>
       </c>
       <c r="AD35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE35">
         <v>9</v>
       </c>
       <c r="AF35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG35">
         <v>10</v>
@@ -4092,28 +4134,28 @@
         <v>10</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K36">
         <v>-1</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O36">
         <v>-1</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
         <v>-1</v>
@@ -4140,7 +4182,7 @@
         <v>-1</v>
       </c>
       <c r="Z36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA36">
         <v>6</v>
@@ -4149,7 +4191,7 @@
         <v>8</v>
       </c>
       <c r="AC36">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AD36">
         <v>6</v>
@@ -4158,7 +4200,7 @@
         <v>6</v>
       </c>
       <c r="AF36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG36">
         <v>10</v>
@@ -4193,28 +4235,28 @@
         <v>10</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K37">
         <v>-1</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O37">
         <v>-1</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
         <v>-1</v>
@@ -4253,13 +4295,13 @@
         <v>10</v>
       </c>
       <c r="AD37">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE37">
         <v>8</v>
       </c>
       <c r="AF37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG37">
         <v>10</v>
@@ -4294,28 +4336,28 @@
         <v>5</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K38">
         <v>-1</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O38">
         <v>-1</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R38">
         <v>-1</v>
@@ -4342,7 +4384,7 @@
         <v>-1</v>
       </c>
       <c r="Z38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA38">
         <v>7</v>
@@ -4351,16 +4393,16 @@
         <v>9</v>
       </c>
       <c r="AC38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE38">
         <v>9</v>
       </c>
       <c r="AF38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG38">
         <v>5</v>
@@ -4395,28 +4437,28 @@
         <v>10</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K39">
         <v>-1</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O39">
         <v>-1</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R39">
         <v>-1</v>
@@ -4443,19 +4485,19 @@
         <v>-1</v>
       </c>
       <c r="Z39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA39">
         <v>7</v>
       </c>
       <c r="AB39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD39">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE39">
         <v>7</v>
@@ -4496,28 +4538,28 @@
         <v>10</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K40">
         <v>-1</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O40">
         <v>-1</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R40">
         <v>-1</v>
@@ -4544,7 +4586,7 @@
         <v>-1</v>
       </c>
       <c r="Z40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA40">
         <v>7</v>
@@ -4553,10 +4595,10 @@
         <v>9</v>
       </c>
       <c r="AC40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE40">
         <v>7</v>
@@ -4565,7 +4607,7 @@
         <v>10</v>
       </c>
       <c r="AG40">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:33">
@@ -4597,28 +4639,28 @@
         <v>10</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K41">
         <v>-1</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O41">
         <v>-1</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R41">
         <v>-1</v>
@@ -4651,13 +4693,13 @@
         <v>7</v>
       </c>
       <c r="AB41">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC41">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD41">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE41">
         <v>6</v>
@@ -4698,28 +4740,28 @@
         <v>10</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K42">
         <v>-1</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O42">
         <v>-1</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R42">
         <v>-1</v>
@@ -4752,19 +4794,19 @@
         <v>8</v>
       </c>
       <c r="AB42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC42">
         <v>10</v>
       </c>
       <c r="AD42">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE42">
         <v>7</v>
       </c>
       <c r="AF42">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG42">
         <v>10</v>
@@ -4799,28 +4841,28 @@
         <v>10</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K43">
         <v>-1</v>
       </c>
       <c r="L43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O43">
         <v>-1</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R43">
         <v>-1</v>
@@ -4859,13 +4901,13 @@
         <v>10</v>
       </c>
       <c r="AD43">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE43">
         <v>9</v>
       </c>
       <c r="AF43">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG43">
         <v>10</v>
@@ -5117,7 +5159,7 @@
         <v>100</v>
       </c>
       <c r="L5">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M5">
         <v>100</v>
@@ -5129,7 +5171,7 @@
         <v>100</v>
       </c>
       <c r="P5">
-        <v>70</v>
+        <v>79.5</v>
       </c>
       <c r="Q5">
         <v>100</v>
@@ -5141,7 +5183,7 @@
         <v>100</v>
       </c>
       <c r="T5">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="U5">
         <v>100</v>
@@ -5153,7 +5195,7 @@
         <v>100</v>
       </c>
       <c r="X5">
-        <v>70</v>
+        <v>79.5</v>
       </c>
       <c r="Y5">
         <v>100</v>
@@ -5271,7 +5313,7 @@
         <v>86.7</v>
       </c>
       <c r="L7">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="M7">
         <v>100</v>
@@ -5283,7 +5325,7 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="Q7">
         <v>100</v>
@@ -5295,7 +5337,7 @@
         <v>86.7</v>
       </c>
       <c r="T7">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U7">
         <v>100</v>
@@ -5307,7 +5349,7 @@
         <v>100</v>
       </c>
       <c r="X7">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="Y7">
         <v>100</v>
@@ -5360,7 +5402,7 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Q8">
         <v>100</v>
@@ -5384,7 +5426,7 @@
         <v>100</v>
       </c>
       <c r="X8">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Y8">
         <v>100</v>
@@ -5502,7 +5544,7 @@
         <v>100</v>
       </c>
       <c r="L10">
-        <v>91.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="M10">
         <v>100</v>
@@ -5514,10 +5556,10 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>70</v>
+        <v>77.3</v>
       </c>
       <c r="Q10">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="R10">
         <v>100</v>
@@ -5526,7 +5568,7 @@
         <v>100</v>
       </c>
       <c r="T10">
-        <v>91.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="U10">
         <v>100</v>
@@ -5538,10 +5580,10 @@
         <v>100</v>
       </c>
       <c r="X10">
-        <v>70</v>
+        <v>77.3</v>
       </c>
       <c r="Y10">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -5579,19 +5621,19 @@
         <v>86.7</v>
       </c>
       <c r="L11">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="M11">
         <v>100</v>
       </c>
       <c r="N11">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="O11">
         <v>100</v>
       </c>
       <c r="P11">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -5603,19 +5645,19 @@
         <v>86.7</v>
       </c>
       <c r="T11">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U11">
         <v>100</v>
       </c>
       <c r="V11">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="W11">
         <v>100</v>
       </c>
       <c r="X11">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Y11">
         <v>100</v>
@@ -5668,7 +5710,7 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -5692,7 +5734,7 @@
         <v>100</v>
       </c>
       <c r="X12">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Y12">
         <v>100</v>
@@ -5733,7 +5775,7 @@
         <v>100</v>
       </c>
       <c r="L13">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="M13">
         <v>100</v>
@@ -5757,7 +5799,7 @@
         <v>100</v>
       </c>
       <c r="T13">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="U13">
         <v>100</v>
@@ -5822,7 +5864,7 @@
         <v>100</v>
       </c>
       <c r="P14">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -5846,7 +5888,7 @@
         <v>100</v>
       </c>
       <c r="X14">
-        <v>95</v>
+        <v>97.7</v>
       </c>
       <c r="Y14">
         <v>100</v>
@@ -5887,7 +5929,7 @@
         <v>100</v>
       </c>
       <c r="L15">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M15">
         <v>100</v>
@@ -5911,7 +5953,7 @@
         <v>100</v>
       </c>
       <c r="T15">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="U15">
         <v>100</v>
@@ -5964,7 +6006,7 @@
         <v>100</v>
       </c>
       <c r="L16">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M16">
         <v>100</v>
@@ -5988,7 +6030,7 @@
         <v>100</v>
       </c>
       <c r="T16">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="U16">
         <v>100</v>
@@ -6041,7 +6083,7 @@
         <v>100</v>
       </c>
       <c r="L17">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="M17">
         <v>100</v>
@@ -6065,7 +6107,7 @@
         <v>100</v>
       </c>
       <c r="T17">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="U17">
         <v>100</v>
@@ -6118,19 +6160,19 @@
         <v>100</v>
       </c>
       <c r="L18">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="M18">
         <v>100</v>
       </c>
       <c r="N18">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="O18">
         <v>100</v>
       </c>
       <c r="P18">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -6142,19 +6184,19 @@
         <v>100</v>
       </c>
       <c r="T18">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="U18">
         <v>100</v>
       </c>
       <c r="V18">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="W18">
         <v>100</v>
       </c>
       <c r="X18">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Y18">
         <v>100</v>
@@ -6195,19 +6237,19 @@
         <v>86.7</v>
       </c>
       <c r="L19">
-        <v>91.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="M19">
         <v>100</v>
       </c>
       <c r="N19">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="O19">
         <v>100</v>
       </c>
       <c r="P19">
-        <v>75</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="Q19">
         <v>100</v>
@@ -6219,19 +6261,19 @@
         <v>86.7</v>
       </c>
       <c r="T19">
-        <v>91.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="U19">
         <v>100</v>
       </c>
       <c r="V19">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="W19">
         <v>100</v>
       </c>
       <c r="X19">
-        <v>75</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="Y19">
         <v>100</v>
@@ -6503,7 +6545,7 @@
         <v>100</v>
       </c>
       <c r="L23">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="M23">
         <v>100</v>
@@ -6527,7 +6569,7 @@
         <v>100</v>
       </c>
       <c r="T23">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U23">
         <v>100</v>
@@ -6580,19 +6622,19 @@
         <v>100</v>
       </c>
       <c r="L24">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M24">
         <v>100</v>
       </c>
       <c r="N24">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="O24">
         <v>100</v>
       </c>
       <c r="P24">
-        <v>85</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Q24">
         <v>100</v>
@@ -6604,19 +6646,19 @@
         <v>100</v>
       </c>
       <c r="T24">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="U24">
         <v>100</v>
       </c>
       <c r="V24">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="W24">
         <v>100</v>
       </c>
       <c r="X24">
-        <v>85</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Y24">
         <v>100</v>
@@ -6669,7 +6711,7 @@
         <v>100</v>
       </c>
       <c r="P25">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Q25">
         <v>100</v>
@@ -6693,7 +6735,7 @@
         <v>100</v>
       </c>
       <c r="X25">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Y25">
         <v>100</v>
@@ -6746,7 +6788,7 @@
         <v>100</v>
       </c>
       <c r="P26">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Q26">
         <v>100</v>
@@ -6770,7 +6812,7 @@
         <v>100</v>
       </c>
       <c r="X26">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Y26">
         <v>100</v>
@@ -6817,7 +6859,7 @@
         <v>100</v>
       </c>
       <c r="N27">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="O27">
         <v>100</v>
@@ -6841,7 +6883,7 @@
         <v>100</v>
       </c>
       <c r="V27">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="W27">
         <v>100</v>
@@ -6900,7 +6942,7 @@
         <v>100</v>
       </c>
       <c r="P28">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Q28">
         <v>100</v>
@@ -6924,7 +6966,7 @@
         <v>100</v>
       </c>
       <c r="X28">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Y28">
         <v>100</v>
@@ -6977,7 +7019,7 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>95</v>
+        <v>95.5</v>
       </c>
       <c r="Q29">
         <v>100</v>
@@ -7001,7 +7043,7 @@
         <v>100</v>
       </c>
       <c r="X29">
-        <v>95</v>
+        <v>95.5</v>
       </c>
       <c r="Y29">
         <v>100</v>
@@ -7042,19 +7084,19 @@
         <v>86.7</v>
       </c>
       <c r="L30">
-        <v>95.8</v>
+        <v>79.5</v>
       </c>
       <c r="M30">
         <v>100</v>
       </c>
       <c r="N30">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="O30">
         <v>100</v>
       </c>
       <c r="P30">
-        <v>95</v>
+        <v>95.5</v>
       </c>
       <c r="Q30">
         <v>100</v>
@@ -7066,19 +7108,19 @@
         <v>86.7</v>
       </c>
       <c r="T30">
-        <v>95.8</v>
+        <v>79.5</v>
       </c>
       <c r="U30">
         <v>100</v>
       </c>
       <c r="V30">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="W30">
         <v>100</v>
       </c>
       <c r="X30">
-        <v>95</v>
+        <v>95.5</v>
       </c>
       <c r="Y30">
         <v>100</v>
@@ -7119,7 +7161,7 @@
         <v>100</v>
       </c>
       <c r="L31">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="M31">
         <v>100</v>
@@ -7143,7 +7185,7 @@
         <v>100</v>
       </c>
       <c r="T31">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U31">
         <v>100</v>
@@ -7350,7 +7392,7 @@
         <v>100</v>
       </c>
       <c r="L34">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M34">
         <v>100</v>
@@ -7374,7 +7416,7 @@
         <v>100</v>
       </c>
       <c r="T34">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="U34">
         <v>100</v>
@@ -7516,7 +7558,7 @@
         <v>100</v>
       </c>
       <c r="P36">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Q36">
         <v>100</v>
@@ -7540,7 +7582,7 @@
         <v>100</v>
       </c>
       <c r="X36">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Y36">
         <v>100</v>
@@ -7812,7 +7854,7 @@
         <v>100</v>
       </c>
       <c r="L40">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="M40">
         <v>100</v>
@@ -7836,7 +7878,7 @@
         <v>100</v>
       </c>
       <c r="T40">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U40">
         <v>100</v>
@@ -7889,7 +7931,7 @@
         <v>100</v>
       </c>
       <c r="L41">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M41">
         <v>100</v>
@@ -7913,7 +7955,7 @@
         <v>100</v>
       </c>
       <c r="T41">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U41">
         <v>100</v>
@@ -8148,19 +8190,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2" s="2">
-        <v>72.5</v>
+        <v>75</v>
       </c>
       <c r="G2" s="2">
-        <v>27.5</v>
+        <v>25</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -8212,19 +8254,19 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" s="2">
-        <v>80</v>
+        <v>77.5</v>
       </c>
       <c r="G4" s="2">
-        <v>20</v>
+        <v>22.5</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -8256,7 +8298,7 @@
         <v>17.5</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>7.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -8267,7 +8309,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
         <v>70</v>
@@ -8288,7 +8330,7 @@
         <v>15</v>
       </c>
       <c r="H6">
-        <v>8.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -8299,7 +8341,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>71</v>
@@ -8308,19 +8350,19 @@
         <v>40</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F7" s="2">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="G7" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H7">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -8363,7 +8405,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
         <v>73</v>
@@ -8384,7 +8426,7 @@
         <v>2.5</v>
       </c>
       <c r="H9">
-        <v>9.9</v>
+        <v>7.2</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -8434,7 +8476,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8472,10 +8514,10 @@
         <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -8495,10 +8537,10 @@
         <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -8518,10 +8560,10 @@
         <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -8541,10 +8583,10 @@
         <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -8564,10 +8606,10 @@
         <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -8581,22 +8623,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920140</v>
+        <v>24330051920026</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="E7" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -8607,19 +8649,19 @@
         <v>24330051920137</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -8627,22 +8669,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920027</v>
+        <v>24330051920137</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -8650,24 +8692,185 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920002</v>
+        <v>24330051920012</v>
       </c>
       <c r="B10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" t="s">
+        <v>70</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>24330051920324</v>
+      </c>
+      <c r="B11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" t="s">
+        <v>106</v>
+      </c>
+      <c r="E11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>24330051920353</v>
+      </c>
+      <c r="B12" t="s">
         <v>84</v>
       </c>
-      <c r="C10" t="s">
-        <v>91</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="C12" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" t="s">
+        <v>107</v>
+      </c>
+      <c r="E12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" t="s">
+        <v>67</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>24330051920140</v>
+      </c>
+      <c r="B13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" t="s">
+        <v>97</v>
+      </c>
+      <c r="D13" t="s">
+        <v>108</v>
+      </c>
+      <c r="E13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" t="s">
+        <v>68</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>24330051920325</v>
+      </c>
+      <c r="B14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" t="s">
         <v>98</v>
       </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>66</v>
-      </c>
-      <c r="G10">
+      <c r="D14" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>24330051920025</v>
+      </c>
+      <c r="B15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" t="s">
+        <v>110</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" t="s">
+        <v>70</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>24330051920027</v>
+      </c>
+      <c r="B16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" t="s">
+        <v>99</v>
+      </c>
+      <c r="D16" t="s">
+        <v>111</v>
+      </c>
+      <c r="E16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" t="s">
+        <v>70</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>24330051920001</v>
+      </c>
+      <c r="B17" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" t="s">
+        <v>112</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" t="s">
+        <v>70</v>
+      </c>
+      <c r="G17">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1AM - Estadisticos 20241.xlsx
+++ b/grupos/1AM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="113">
   <si>
     <t>Materia</t>
   </si>
@@ -221,12 +221,12 @@
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
@@ -257,33 +257,33 @@
     <t>ESCOBAR</t>
   </si>
   <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>CUICAHUA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
+    <t>MENCIAS</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>REYES</t>
   </si>
   <si>
     <t>RUIZ</t>
   </si>
   <si>
-    <t>CUICAHUA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>MENCIAS</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
@@ -293,30 +293,30 @@
     <t>JUAN</t>
   </si>
   <si>
+    <t>CALIHUA</t>
+  </si>
+  <si>
+    <t>GIL</t>
+  </si>
+  <si>
+    <t>TINOCO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>ADRIAN</t>
   </si>
   <si>
-    <t>CALIHUA</t>
+    <t>JORGE</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
   </si>
   <si>
     <t>SANTOS</t>
   </si>
   <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>JORGE</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
     <t>TEZOCO</t>
   </si>
   <si>
@@ -326,31 +326,31 @@
     <t>GIOVANNI ARIEL</t>
   </si>
   <si>
+    <t>JESUS ANTONIO</t>
+  </si>
+  <si>
+    <t>PABLO AZAEL</t>
+  </si>
+  <si>
+    <t>ANGEL MOISES</t>
+  </si>
+  <si>
+    <t>JOY JARA</t>
+  </si>
+  <si>
     <t>JOHANAN</t>
   </si>
   <si>
-    <t>JESUS ANTONIO</t>
+    <t>JAVIER</t>
+  </si>
+  <si>
+    <t>IAN</t>
+  </si>
+  <si>
+    <t>EDGAR</t>
   </si>
   <si>
     <t>ALEXIS URIEL</t>
-  </si>
-  <si>
-    <t>PABLO AZAEL</t>
-  </si>
-  <si>
-    <t>ANGEL MOISES</t>
-  </si>
-  <si>
-    <t>JOY JARA</t>
-  </si>
-  <si>
-    <t>JAVIER</t>
-  </si>
-  <si>
-    <t>IAN</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
   </si>
   <si>
     <t>OSMAR EDUARDO</t>
@@ -905,7 +905,7 @@
         <v>9</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
         <v>8</v>
@@ -917,7 +917,7 @@
         <v>9</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
         <v>8</v>
@@ -953,7 +953,7 @@
         <v>9</v>
       </c>
       <c r="AA4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB4">
         <v>9</v>
@@ -1006,7 +1006,7 @@
         <v>6</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L5">
         <v>7</v>
@@ -1018,7 +1018,7 @@
         <v>8</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
         <v>6</v>
@@ -1066,7 +1066,7 @@
         <v>7</v>
       </c>
       <c r="AE5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF5">
         <v>5</v>
@@ -1107,7 +1107,7 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
         <v>10</v>
@@ -1119,7 +1119,7 @@
         <v>9</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
         <v>10</v>
@@ -1155,7 +1155,7 @@
         <v>10</v>
       </c>
       <c r="AA6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB6">
         <v>10</v>
@@ -1208,7 +1208,7 @@
         <v>8</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
         <v>7</v>
@@ -1220,7 +1220,7 @@
         <v>6</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P7">
         <v>8</v>
@@ -1268,7 +1268,7 @@
         <v>6</v>
       </c>
       <c r="AE7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF7">
         <v>9</v>
@@ -1309,7 +1309,7 @@
         <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
         <v>9</v>
@@ -1321,7 +1321,7 @@
         <v>6</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
         <v>8</v>
@@ -1410,7 +1410,7 @@
         <v>10</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
         <v>10</v>
@@ -1422,7 +1422,7 @@
         <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P9">
         <v>10</v>
@@ -1470,7 +1470,7 @@
         <v>9</v>
       </c>
       <c r="AE9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF9">
         <v>10</v>
@@ -1511,7 +1511,7 @@
         <v>5</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L10">
         <v>5</v>
@@ -1523,7 +1523,7 @@
         <v>6</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P10">
         <v>5</v>
@@ -1571,7 +1571,7 @@
         <v>6</v>
       </c>
       <c r="AE10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF10">
         <v>5</v>
@@ -1612,7 +1612,7 @@
         <v>6</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L11">
         <v>6</v>
@@ -1624,7 +1624,7 @@
         <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P11">
         <v>7</v>
@@ -1713,7 +1713,7 @@
         <v>8</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L12">
         <v>10</v>
@@ -1725,7 +1725,7 @@
         <v>8</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P12">
         <v>9</v>
@@ -1773,7 +1773,7 @@
         <v>8</v>
       </c>
       <c r="AE12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF12">
         <v>8</v>
@@ -1814,7 +1814,7 @@
         <v>8</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L13">
         <v>9</v>
@@ -1826,7 +1826,7 @@
         <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P13">
         <v>10</v>
@@ -1862,7 +1862,7 @@
         <v>8</v>
       </c>
       <c r="AA13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB13">
         <v>10</v>
@@ -1915,7 +1915,7 @@
         <v>10</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
         <v>9</v>
@@ -1927,7 +1927,7 @@
         <v>8</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P14">
         <v>9</v>
@@ -1975,7 +1975,7 @@
         <v>8</v>
       </c>
       <c r="AE14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF14">
         <v>8</v>
@@ -2016,7 +2016,7 @@
         <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
         <v>7</v>
@@ -2028,7 +2028,7 @@
         <v>8</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P15">
         <v>8</v>
@@ -2117,7 +2117,7 @@
         <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
         <v>7</v>
@@ -2129,7 +2129,7 @@
         <v>6</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
         <v>8</v>
@@ -2165,7 +2165,7 @@
         <v>5</v>
       </c>
       <c r="AA16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB16">
         <v>8</v>
@@ -2218,7 +2218,7 @@
         <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L17">
         <v>8</v>
@@ -2230,7 +2230,7 @@
         <v>7</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P17">
         <v>5</v>
@@ -2278,7 +2278,7 @@
         <v>7</v>
       </c>
       <c r="AE17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF17">
         <v>5</v>
@@ -2319,7 +2319,7 @@
         <v>6</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L18">
         <v>6</v>
@@ -2331,7 +2331,7 @@
         <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P18">
         <v>6</v>
@@ -2420,7 +2420,7 @@
         <v>5</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L19">
         <v>6</v>
@@ -2432,7 +2432,7 @@
         <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P19">
         <v>6</v>
@@ -2521,7 +2521,7 @@
         <v>7</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L20">
         <v>9</v>
@@ -2533,7 +2533,7 @@
         <v>7</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P20">
         <v>10</v>
@@ -2569,7 +2569,7 @@
         <v>7</v>
       </c>
       <c r="AA20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB20">
         <v>10</v>
@@ -2581,7 +2581,7 @@
         <v>7</v>
       </c>
       <c r="AE20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF20">
         <v>9</v>
@@ -2622,7 +2622,7 @@
         <v>8</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
         <v>8</v>
@@ -2634,7 +2634,7 @@
         <v>8</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P21">
         <v>10</v>
@@ -2670,7 +2670,7 @@
         <v>8</v>
       </c>
       <c r="AA21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB21">
         <v>9</v>
@@ -2682,7 +2682,7 @@
         <v>7</v>
       </c>
       <c r="AE21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF21">
         <v>9</v>
@@ -2723,7 +2723,7 @@
         <v>7</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
         <v>10</v>
@@ -2735,7 +2735,7 @@
         <v>8</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
         <v>9</v>
@@ -2824,7 +2824,7 @@
         <v>8</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
         <v>9</v>
@@ -2836,7 +2836,7 @@
         <v>7</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
         <v>8</v>
@@ -2872,7 +2872,7 @@
         <v>8</v>
       </c>
       <c r="AA23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB23">
         <v>9</v>
@@ -2884,7 +2884,7 @@
         <v>7</v>
       </c>
       <c r="AE23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF23">
         <v>8</v>
@@ -2925,7 +2925,7 @@
         <v>5</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L24">
         <v>6</v>
@@ -2937,7 +2937,7 @@
         <v>8</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P24">
         <v>5</v>
@@ -2985,7 +2985,7 @@
         <v>6</v>
       </c>
       <c r="AE24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF24">
         <v>5</v>
@@ -3026,7 +3026,7 @@
         <v>6</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L25">
         <v>8</v>
@@ -3038,7 +3038,7 @@
         <v>7</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P25">
         <v>6</v>
@@ -3086,7 +3086,7 @@
         <v>7</v>
       </c>
       <c r="AE25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AF25">
         <v>6</v>
@@ -3127,7 +3127,7 @@
         <v>6</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L26">
         <v>8</v>
@@ -3139,7 +3139,7 @@
         <v>7</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
         <v>8</v>
@@ -3187,7 +3187,7 @@
         <v>7</v>
       </c>
       <c r="AE26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF26">
         <v>9</v>
@@ -3228,7 +3228,7 @@
         <v>6</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L27">
         <v>7</v>
@@ -3240,7 +3240,7 @@
         <v>8</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P27">
         <v>6</v>
@@ -3288,7 +3288,7 @@
         <v>6</v>
       </c>
       <c r="AE27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF27">
         <v>5</v>
@@ -3329,7 +3329,7 @@
         <v>5</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L28">
         <v>7</v>
@@ -3341,7 +3341,7 @@
         <v>8</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
         <v>9</v>
@@ -3377,7 +3377,7 @@
         <v>5</v>
       </c>
       <c r="AA28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB28">
         <v>7</v>
@@ -3389,7 +3389,7 @@
         <v>7</v>
       </c>
       <c r="AE28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF28">
         <v>9</v>
@@ -3430,7 +3430,7 @@
         <v>8</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L29">
         <v>9</v>
@@ -3442,7 +3442,7 @@
         <v>7</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P29">
         <v>6</v>
@@ -3490,7 +3490,7 @@
         <v>7</v>
       </c>
       <c r="AE29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF29">
         <v>5</v>
@@ -3531,7 +3531,7 @@
         <v>5</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L30">
         <v>6</v>
@@ -3543,7 +3543,7 @@
         <v>8</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P30">
         <v>6</v>
@@ -3632,7 +3632,7 @@
         <v>5</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L31">
         <v>5</v>
@@ -3644,7 +3644,7 @@
         <v>8</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P31">
         <v>8</v>
@@ -3733,7 +3733,7 @@
         <v>9</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L32">
         <v>9</v>
@@ -3745,7 +3745,7 @@
         <v>7</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P32">
         <v>10</v>
@@ -3793,7 +3793,7 @@
         <v>7</v>
       </c>
       <c r="AE32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF32">
         <v>10</v>
@@ -3834,7 +3834,7 @@
         <v>9</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L33">
         <v>9</v>
@@ -3846,7 +3846,7 @@
         <v>9</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P33">
         <v>9</v>
@@ -3882,7 +3882,7 @@
         <v>9</v>
       </c>
       <c r="AA33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB33">
         <v>9</v>
@@ -3894,7 +3894,7 @@
         <v>8</v>
       </c>
       <c r="AE33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF33">
         <v>9</v>
@@ -3935,7 +3935,7 @@
         <v>5</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L34">
         <v>9</v>
@@ -3947,7 +3947,7 @@
         <v>8</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P34">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>5</v>
       </c>
       <c r="AA34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB34">
         <v>9</v>
@@ -3995,7 +3995,7 @@
         <v>7</v>
       </c>
       <c r="AE34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF34">
         <v>8</v>
@@ -4036,7 +4036,7 @@
         <v>9</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L35">
         <v>9</v>
@@ -4048,7 +4048,7 @@
         <v>8</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P35">
         <v>10</v>
@@ -4084,7 +4084,7 @@
         <v>9</v>
       </c>
       <c r="AA35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB35">
         <v>10</v>
@@ -4096,7 +4096,7 @@
         <v>8</v>
       </c>
       <c r="AE35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF35">
         <v>9</v>
@@ -4137,7 +4137,7 @@
         <v>9</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L36">
         <v>8</v>
@@ -4149,7 +4149,7 @@
         <v>6</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P36">
         <v>9</v>
@@ -4185,7 +4185,7 @@
         <v>8</v>
       </c>
       <c r="AA36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB36">
         <v>8</v>
@@ -4197,7 +4197,7 @@
         <v>6</v>
       </c>
       <c r="AE36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF36">
         <v>9</v>
@@ -4238,7 +4238,7 @@
         <v>10</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L37">
         <v>10</v>
@@ -4250,7 +4250,7 @@
         <v>8</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P37">
         <v>9</v>
@@ -4298,7 +4298,7 @@
         <v>8</v>
       </c>
       <c r="AE37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF37">
         <v>9</v>
@@ -4339,7 +4339,7 @@
         <v>9</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L38">
         <v>9</v>
@@ -4351,7 +4351,7 @@
         <v>8</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P38">
         <v>9</v>
@@ -4387,7 +4387,7 @@
         <v>9</v>
       </c>
       <c r="AA38">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB38">
         <v>9</v>
@@ -4440,7 +4440,7 @@
         <v>8</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L39">
         <v>10</v>
@@ -4452,7 +4452,7 @@
         <v>8</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P39">
         <v>9</v>
@@ -4488,7 +4488,7 @@
         <v>8</v>
       </c>
       <c r="AA39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB39">
         <v>10</v>
@@ -4500,7 +4500,7 @@
         <v>7</v>
       </c>
       <c r="AE39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF39">
         <v>9</v>
@@ -4541,7 +4541,7 @@
         <v>9</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L40">
         <v>9</v>
@@ -4553,7 +4553,7 @@
         <v>8</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P40">
         <v>10</v>
@@ -4589,7 +4589,7 @@
         <v>9</v>
       </c>
       <c r="AA40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB40">
         <v>9</v>
@@ -4601,7 +4601,7 @@
         <v>7</v>
       </c>
       <c r="AE40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF40">
         <v>10</v>
@@ -4642,7 +4642,7 @@
         <v>6</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L41">
         <v>10</v>
@@ -4654,7 +4654,7 @@
         <v>8</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P41">
         <v>8</v>
@@ -4702,7 +4702,7 @@
         <v>7</v>
       </c>
       <c r="AE41">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF41">
         <v>8</v>
@@ -4743,7 +4743,7 @@
         <v>9</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L42">
         <v>10</v>
@@ -4755,7 +4755,7 @@
         <v>9</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P42">
         <v>10</v>
@@ -4791,7 +4791,7 @@
         <v>9</v>
       </c>
       <c r="AA42">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB42">
         <v>10</v>
@@ -4803,7 +4803,7 @@
         <v>9</v>
       </c>
       <c r="AE42">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF42">
         <v>10</v>
@@ -4844,7 +4844,7 @@
         <v>9</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L43">
         <v>9</v>
@@ -4856,7 +4856,7 @@
         <v>8</v>
       </c>
       <c r="O43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P43">
         <v>10</v>
@@ -4904,7 +4904,7 @@
         <v>8</v>
       </c>
       <c r="AE43">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF43">
         <v>10</v>
@@ -5310,7 +5310,7 @@
         <v>100</v>
       </c>
       <c r="K7">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="L7">
         <v>95.5</v>
@@ -5334,7 +5334,7 @@
         <v>100</v>
       </c>
       <c r="S7">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="T7">
         <v>95.5</v>
@@ -5387,7 +5387,7 @@
         <v>100</v>
       </c>
       <c r="K8">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L8">
         <v>100</v>
@@ -5411,7 +5411,7 @@
         <v>100</v>
       </c>
       <c r="S8">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="T8">
         <v>100</v>
@@ -5541,7 +5541,7 @@
         <v>100</v>
       </c>
       <c r="K10">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="L10">
         <v>86.40000000000001</v>
@@ -5565,7 +5565,7 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="T10">
         <v>86.40000000000001</v>
@@ -5618,7 +5618,7 @@
         <v>100</v>
       </c>
       <c r="K11">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="L11">
         <v>95.5</v>
@@ -5642,7 +5642,7 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="T11">
         <v>95.5</v>
@@ -6234,7 +6234,7 @@
         <v>100</v>
       </c>
       <c r="K19">
-        <v>86.7</v>
+        <v>90</v>
       </c>
       <c r="L19">
         <v>88.59999999999999</v>
@@ -6258,7 +6258,7 @@
         <v>100</v>
       </c>
       <c r="S19">
-        <v>86.7</v>
+        <v>90</v>
       </c>
       <c r="T19">
         <v>88.59999999999999</v>
@@ -6850,7 +6850,7 @@
         <v>100</v>
       </c>
       <c r="K27">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="L27">
         <v>100</v>
@@ -6874,7 +6874,7 @@
         <v>100</v>
       </c>
       <c r="S27">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="T27">
         <v>100</v>
@@ -7081,7 +7081,7 @@
         <v>100</v>
       </c>
       <c r="K30">
-        <v>86.7</v>
+        <v>90</v>
       </c>
       <c r="L30">
         <v>79.5</v>
@@ -7105,7 +7105,7 @@
         <v>100</v>
       </c>
       <c r="S30">
-        <v>86.7</v>
+        <v>90</v>
       </c>
       <c r="T30">
         <v>79.5</v>
@@ -8213,7 +8213,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
@@ -8234,7 +8234,7 @@
         <v>22.5</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -8245,7 +8245,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
@@ -8254,19 +8254,19 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2">
-        <v>77.5</v>
+        <v>82.5</v>
       </c>
       <c r="G4" s="2">
-        <v>22.5</v>
+        <v>17.5</v>
       </c>
       <c r="H4">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -8382,19 +8382,19 @@
         <v>40</v>
       </c>
       <c r="D8">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" s="2">
-        <v>92.5</v>
+        <v>90</v>
       </c>
       <c r="G8" s="2">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="H8">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -8476,7 +8476,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8523,7 +8523,7 @@
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -8554,7 +8554,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920141</v>
+        <v>24330051920026</v>
       </c>
       <c r="B4" t="s">
         <v>79</v>
@@ -8566,7 +8566,7 @@
         <v>102</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
         <v>67</v>
@@ -8577,7 +8577,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920141</v>
+        <v>24330051920026</v>
       </c>
       <c r="B5" t="s">
         <v>79</v>
@@ -8600,7 +8600,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920026</v>
+        <v>24330051920012</v>
       </c>
       <c r="B6" t="s">
         <v>80</v>
@@ -8612,10 +8612,10 @@
         <v>103</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -8623,22 +8623,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920026</v>
+        <v>24330051920324</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -8646,19 +8646,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920137</v>
+        <v>24330051920353</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
         <v>68</v>
@@ -8669,22 +8669,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920137</v>
+        <v>24330051920141</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -8692,22 +8692,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920012</v>
+        <v>24330051920140</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -8715,16 +8715,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920324</v>
+        <v>24330051920325</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D11" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E11" t="s">
         <v>11</v>
@@ -8738,22 +8738,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920353</v>
+        <v>24330051920025</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="D12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F12" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -8761,22 +8761,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920140</v>
+        <v>24330051920137</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="E13" t="s">
         <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -8784,22 +8784,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920325</v>
+        <v>24330051920027</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C14" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F14" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -8807,16 +8807,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920025</v>
+        <v>24330051920001</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E15" t="s">
         <v>12</v>
@@ -8825,52 +8825,6 @@
         <v>70</v>
       </c>
       <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>24330051920027</v>
-      </c>
-      <c r="B16" t="s">
-        <v>88</v>
-      </c>
-      <c r="C16" t="s">
-        <v>99</v>
-      </c>
-      <c r="D16" t="s">
-        <v>111</v>
-      </c>
-      <c r="E16" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" t="s">
-        <v>70</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>24330051920001</v>
-      </c>
-      <c r="B17" t="s">
-        <v>89</v>
-      </c>
-      <c r="C17" t="s">
-        <v>100</v>
-      </c>
-      <c r="D17" t="s">
-        <v>112</v>
-      </c>
-      <c r="E17" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" t="s">
-        <v>70</v>
-      </c>
-      <c r="G17">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1AM - Estadisticos 20241.xlsx
+++ b/grupos/1AM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="110">
   <si>
     <t>Materia</t>
   </si>
@@ -254,6 +254,15 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
     <t>ESCOBAR</t>
   </si>
   <si>
@@ -278,6 +287,15 @@
     <t>RUIZ</t>
   </si>
   <si>
+    <t>OROZCO</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
     <t>JUAN</t>
   </si>
   <si>
@@ -300,6 +318,12 @@
   </si>
   <si>
     <t>SANTOS</t>
+  </si>
+  <si>
+    <t>ANGEL ALEXANDER</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
   </si>
   <si>
     <t>GIOVANNI ARIEL</t>
@@ -7563,7 +7587,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7595,22 +7619,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920103</v>
+        <v>24330051920328</v>
       </c>
       <c r="B2" t="s">
         <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7618,16 +7642,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920103</v>
+        <v>24330051920328</v>
       </c>
       <c r="B3" t="s">
         <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -7641,22 +7665,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920026</v>
+        <v>24330051920328</v>
       </c>
       <c r="B4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7664,22 +7688,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920026</v>
+        <v>24330051920328</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7687,22 +7711,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920324</v>
+        <v>24330051920326</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7710,16 +7734,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920353</v>
+        <v>24330051920326</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
@@ -7733,16 +7757,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920141</v>
+        <v>24330051920326</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
         <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -7756,22 +7780,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920140</v>
+        <v>24330051920326</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7779,22 +7803,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920325</v>
+        <v>24330051920233</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7802,24 +7826,277 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
+        <v>24330051920233</v>
+      </c>
+      <c r="B11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>24330051920233</v>
+      </c>
+      <c r="B12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C12" t="s">
+        <v>91</v>
+      </c>
+      <c r="D12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>24330051920103</v>
+      </c>
+      <c r="B13" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D13" t="s">
+        <v>102</v>
+      </c>
+      <c r="E13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" t="s">
+        <v>67</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>24330051920103</v>
+      </c>
+      <c r="B14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" t="s">
+        <v>102</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>66</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>24330051920026</v>
+      </c>
+      <c r="B15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D15" t="s">
+        <v>103</v>
+      </c>
+      <c r="E15" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" t="s">
+        <v>67</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>24330051920026</v>
+      </c>
+      <c r="B16" t="s">
+        <v>82</v>
+      </c>
+      <c r="C16" t="s">
+        <v>93</v>
+      </c>
+      <c r="D16" t="s">
+        <v>103</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>66</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>24330051920324</v>
+      </c>
+      <c r="B17" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D17" t="s">
+        <v>104</v>
+      </c>
+      <c r="E17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" t="s">
+        <v>69</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>24330051920353</v>
+      </c>
+      <c r="B18" t="s">
+        <v>84</v>
+      </c>
+      <c r="C18" t="s">
+        <v>95</v>
+      </c>
+      <c r="D18" t="s">
+        <v>105</v>
+      </c>
+      <c r="E18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>24330051920141</v>
+      </c>
+      <c r="B19" t="s">
+        <v>85</v>
+      </c>
+      <c r="C19" t="s">
+        <v>96</v>
+      </c>
+      <c r="D19" t="s">
+        <v>106</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>66</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>24330051920140</v>
+      </c>
+      <c r="B20" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" t="s">
+        <v>97</v>
+      </c>
+      <c r="D20" t="s">
+        <v>107</v>
+      </c>
+      <c r="E20" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" t="s">
+        <v>67</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>24330051920325</v>
+      </c>
+      <c r="B21" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" t="s">
+        <v>98</v>
+      </c>
+      <c r="D21" t="s">
+        <v>108</v>
+      </c>
+      <c r="E21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" t="s">
+        <v>69</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
         <v>24330051920137</v>
       </c>
-      <c r="B11" t="s">
-        <v>85</v>
-      </c>
-      <c r="C11" t="s">
-        <v>93</v>
-      </c>
-      <c r="D11" t="s">
-        <v>101</v>
-      </c>
-      <c r="E11" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="B22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" t="s">
+        <v>99</v>
+      </c>
+      <c r="D22" t="s">
+        <v>109</v>
+      </c>
+      <c r="E22" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" t="s">
         <v>67</v>
       </c>
-      <c r="G11">
+      <c r="G22">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1AM - Estadisticos 20241.xlsx
+++ b/grupos/1AM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="112">
   <si>
     <t>Materia</t>
   </si>
@@ -221,24 +221,24 @@
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
+    <t>Herrera Serrano Mayra Iliana</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
-    <t>Herrera Serrano Mayra Iliana</t>
-  </si>
-  <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
-  </si>
-  <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
     <t>Faltante Faltante Faltante</t>
   </si>
   <si>
@@ -257,97 +257,103 @@
     <t>CID</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
     <t>MACHORRO</t>
   </si>
   <si>
-    <t>ARELLANO</t>
+    <t>RAZCON</t>
   </si>
   <si>
     <t>ESCOBAR</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>IXMATLAHUA</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MENCIAS</t>
-  </si>
-  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
     <t>OROZCO</t>
   </si>
   <si>
+    <t>RANGEL</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>PAZ</t>
+    <t>ROJAS</t>
   </si>
   <si>
     <t>JUAN</t>
   </si>
   <si>
+    <t>TINOCO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ADRIAN</t>
+  </si>
+  <si>
     <t>CALIHUA</t>
   </si>
   <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ADRIAN</t>
-  </si>
-  <si>
-    <t>JORGE</t>
-  </si>
-  <si>
     <t>MUÑOZ</t>
   </si>
   <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
     <t>ANGEL ALEXANDER</t>
   </si>
   <si>
+    <t>AXEL BENITO</t>
+  </si>
+  <si>
+    <t>YERIEL</t>
+  </si>
+  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
+    <t>JOSE ARTURO</t>
+  </si>
+  <si>
     <t>GIOVANNI ARIEL</t>
   </si>
   <si>
+    <t>ANGEL MOISES</t>
+  </si>
+  <si>
+    <t>JOY JARA</t>
+  </si>
+  <si>
+    <t>JOHANAN</t>
+  </si>
+  <si>
     <t>JESUS ANTONIO</t>
   </si>
   <si>
-    <t>ANGEL MOISES</t>
-  </si>
-  <si>
-    <t>JOY JARA</t>
-  </si>
-  <si>
-    <t>JOHANAN</t>
-  </si>
-  <si>
-    <t>JAVIER</t>
-  </si>
-  <si>
     <t>IAN</t>
-  </si>
-  <si>
-    <t>ALEXIS URIEL</t>
   </si>
 </sst>
 </file>
@@ -895,13 +901,13 @@
         <v>8</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -916,7 +922,7 @@
         <v>-1</v>
       </c>
       <c r="W4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X4">
         <v>9</v>
@@ -984,13 +990,13 @@
         <v>6</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -1005,7 +1011,7 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X5">
         <v>5</v>
@@ -1073,13 +1079,13 @@
         <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
         <v>-1</v>
@@ -1162,13 +1168,13 @@
         <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q7">
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1251,13 +1257,13 @@
         <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -1340,13 +1346,13 @@
         <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1429,13 +1435,13 @@
         <v>5</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q10">
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1518,13 +1524,13 @@
         <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -1545,7 +1551,7 @@
         <v>5</v>
       </c>
       <c r="Y11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z11">
         <v>5</v>
@@ -1607,13 +1613,13 @@
         <v>9</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q12">
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -1628,7 +1634,7 @@
         <v>-1</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X12">
         <v>7</v>
@@ -1696,13 +1702,13 @@
         <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q13">
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1785,13 +1791,13 @@
         <v>9</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -1874,13 +1880,13 @@
         <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -1963,13 +1969,13 @@
         <v>8</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -1984,7 +1990,7 @@
         <v>-1</v>
       </c>
       <c r="W16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>7</v>
@@ -2052,13 +2058,13 @@
         <v>5</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q17">
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -2141,13 +2147,13 @@
         <v>6</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q18">
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -2230,13 +2236,13 @@
         <v>6</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -2251,13 +2257,13 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X19">
         <v>5</v>
       </c>
       <c r="Y19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z19">
         <v>5</v>
@@ -2319,13 +2325,13 @@
         <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
         <v>-1</v>
@@ -2408,13 +2414,13 @@
         <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
         <v>-1</v>
@@ -2429,7 +2435,7 @@
         <v>-1</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X21">
         <v>6</v>
@@ -2497,13 +2503,13 @@
         <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q22">
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
         <v>-1</v>
@@ -2586,13 +2592,13 @@
         <v>8</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
         <v>-1</v>
@@ -2607,7 +2613,7 @@
         <v>-1</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X23">
         <v>8</v>
@@ -2675,13 +2681,13 @@
         <v>5</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q24">
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S24">
         <v>-1</v>
@@ -2696,7 +2702,7 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X24">
         <v>5</v>
@@ -2764,13 +2770,13 @@
         <v>6</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S25">
         <v>-1</v>
@@ -2785,13 +2791,13 @@
         <v>-1</v>
       </c>
       <c r="W25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X25">
         <v>8</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z25">
         <v>5</v>
@@ -2853,13 +2859,13 @@
         <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q26">
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
         <v>-1</v>
@@ -2942,13 +2948,13 @@
         <v>6</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q27">
         <v>-1</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
         <v>-1</v>
@@ -2963,13 +2969,13 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X27">
         <v>5</v>
       </c>
       <c r="Y27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z27">
         <v>5</v>
@@ -3031,13 +3037,13 @@
         <v>9</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q28">
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
         <v>-1</v>
@@ -3052,13 +3058,13 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X28">
         <v>7</v>
       </c>
       <c r="Y28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z28">
         <v>7</v>
@@ -3120,13 +3126,13 @@
         <v>6</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q29">
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
         <v>-1</v>
@@ -3209,13 +3215,13 @@
         <v>6</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q30">
         <v>-1</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S30">
         <v>-1</v>
@@ -3230,13 +3236,13 @@
         <v>-1</v>
       </c>
       <c r="W30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X30">
         <v>5</v>
       </c>
       <c r="Y30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z30">
         <v>5</v>
@@ -3298,13 +3304,13 @@
         <v>8</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q31">
         <v>-1</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S31">
         <v>-1</v>
@@ -3325,7 +3331,7 @@
         <v>6</v>
       </c>
       <c r="Y31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z31">
         <v>7</v>
@@ -3387,13 +3393,13 @@
         <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
         <v>-1</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
         <v>-1</v>
@@ -3476,13 +3482,13 @@
         <v>9</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q33">
         <v>-1</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S33">
         <v>-1</v>
@@ -3565,13 +3571,13 @@
         <v>8</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q34">
         <v>-1</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S34">
         <v>-1</v>
@@ -3586,7 +3592,7 @@
         <v>-1</v>
       </c>
       <c r="W34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X34">
         <v>6</v>
@@ -3654,13 +3660,13 @@
         <v>10</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q35">
         <v>-1</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
         <v>-1</v>
@@ -3743,13 +3749,13 @@
         <v>9</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q36">
         <v>-1</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S36">
         <v>-1</v>
@@ -3770,7 +3776,7 @@
         <v>7</v>
       </c>
       <c r="Y36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z36">
         <v>7</v>
@@ -3832,13 +3838,13 @@
         <v>9</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q37">
         <v>-1</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S37">
         <v>-1</v>
@@ -3921,13 +3927,13 @@
         <v>9</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q38">
         <v>-1</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S38">
         <v>-1</v>
@@ -3942,7 +3948,7 @@
         <v>-1</v>
       </c>
       <c r="W38">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X38">
         <v>8</v>
@@ -4010,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q39">
         <v>-1</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S39">
         <v>-1</v>
@@ -4099,13 +4105,13 @@
         <v>10</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q40">
         <v>-1</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S40">
         <v>-1</v>
@@ -4120,7 +4126,7 @@
         <v>-1</v>
       </c>
       <c r="W40">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X40">
         <v>8</v>
@@ -4188,13 +4194,13 @@
         <v>8</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q41">
         <v>-1</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S41">
         <v>-1</v>
@@ -4277,13 +4283,13 @@
         <v>10</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q42">
         <v>-1</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S42">
         <v>-1</v>
@@ -4298,7 +4304,7 @@
         <v>-1</v>
       </c>
       <c r="W42">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X42">
         <v>9</v>
@@ -4366,13 +4372,13 @@
         <v>10</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q43">
         <v>-1</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S43">
         <v>-1</v>
@@ -4387,7 +4393,7 @@
         <v>-1</v>
       </c>
       <c r="W43">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X43">
         <v>8</v>
@@ -4651,7 +4657,7 @@
         <v>100</v>
       </c>
       <c r="R5">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -4787,7 +4793,7 @@
         <v>93.3</v>
       </c>
       <c r="R7">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S7">
         <v>100</v>
@@ -4991,7 +4997,7 @@
         <v>86.7</v>
       </c>
       <c r="R10">
-        <v>86.40000000000001</v>
+        <v>59.4</v>
       </c>
       <c r="S10">
         <v>100</v>
@@ -5059,7 +5065,7 @@
         <v>93.3</v>
       </c>
       <c r="R11">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S11">
         <v>100</v>
@@ -5195,7 +5201,7 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S13">
         <v>100</v>
@@ -5331,7 +5337,7 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S15">
         <v>100</v>
@@ -5399,7 +5405,7 @@
         <v>100</v>
       </c>
       <c r="R16">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S16">
         <v>100</v>
@@ -5467,7 +5473,7 @@
         <v>100</v>
       </c>
       <c r="R17">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S17">
         <v>100</v>
@@ -5535,7 +5541,7 @@
         <v>100</v>
       </c>
       <c r="R18">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S18">
         <v>100</v>
@@ -5603,7 +5609,7 @@
         <v>90</v>
       </c>
       <c r="R19">
-        <v>88.59999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -5875,7 +5881,7 @@
         <v>100</v>
       </c>
       <c r="R23">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S23">
         <v>100</v>
@@ -5943,7 +5949,7 @@
         <v>100</v>
       </c>
       <c r="R24">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S24">
         <v>100</v>
@@ -6351,7 +6357,7 @@
         <v>90</v>
       </c>
       <c r="R30">
-        <v>79.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="S30">
         <v>100</v>
@@ -6419,7 +6425,7 @@
         <v>100</v>
       </c>
       <c r="R31">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S31">
         <v>100</v>
@@ -6623,7 +6629,7 @@
         <v>100</v>
       </c>
       <c r="R34">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S34">
         <v>100</v>
@@ -7031,7 +7037,7 @@
         <v>100</v>
       </c>
       <c r="R40">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S40">
         <v>100</v>
@@ -7099,7 +7105,7 @@
         <v>100</v>
       </c>
       <c r="R41">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="S41">
         <v>100</v>
@@ -7336,7 +7342,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
@@ -7345,19 +7351,19 @@
         <v>40</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2">
-        <v>77.5</v>
+        <v>82.5</v>
       </c>
       <c r="G3" s="2">
-        <v>22.5</v>
+        <v>17.5</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7368,7 +7374,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
@@ -7389,7 +7395,7 @@
         <v>17.5</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>7.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7400,7 +7406,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>69</v>
@@ -7409,19 +7415,19 @@
         <v>40</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F5" s="2">
-        <v>82.5</v>
+        <v>90</v>
       </c>
       <c r="G5" s="2">
-        <v>17.5</v>
+        <v>10</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7441,16 +7447,16 @@
         <v>40</v>
       </c>
       <c r="D6">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G6" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H6">
         <v>8.5</v>
@@ -7464,7 +7470,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>71</v>
@@ -7473,19 +7479,19 @@
         <v>40</v>
       </c>
       <c r="D7">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>90</v>
+        <v>97.5</v>
       </c>
       <c r="G7" s="2">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="H7">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7496,7 +7502,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
         <v>72</v>
@@ -7517,7 +7523,7 @@
         <v>2.5</v>
       </c>
       <c r="H8">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7587,7 +7593,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7625,16 +7631,16 @@
         <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7648,10 +7654,10 @@
         <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -7671,16 +7677,16 @@
         <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7694,16 +7700,16 @@
         <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7711,19 +7717,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920326</v>
+        <v>24330051920329</v>
       </c>
       <c r="B6" t="s">
         <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
         <v>67</v>
@@ -7734,22 +7740,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920326</v>
+        <v>24330051920329</v>
       </c>
       <c r="B7" t="s">
         <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7757,22 +7763,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920326</v>
+        <v>24330051920329</v>
       </c>
       <c r="B8" t="s">
         <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7780,22 +7786,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920326</v>
+        <v>24330051920329</v>
       </c>
       <c r="B9" t="s">
         <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E9" t="s">
         <v>11</v>
       </c>
       <c r="F9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7803,22 +7809,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920233</v>
+        <v>24330051920145</v>
       </c>
       <c r="B10" t="s">
         <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7826,22 +7832,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920233</v>
+        <v>24330051920145</v>
       </c>
       <c r="B11" t="s">
         <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -7849,22 +7855,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920233</v>
+        <v>24330051920145</v>
       </c>
       <c r="B12" t="s">
         <v>80</v>
       </c>
       <c r="C12" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D12" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -7872,22 +7878,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920103</v>
+        <v>24330051920145</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C13" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -7895,7 +7901,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920103</v>
+        <v>24330051920233</v>
       </c>
       <c r="B14" t="s">
         <v>81</v>
@@ -7904,13 +7910,13 @@
         <v>92</v>
       </c>
       <c r="D14" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -7918,22 +7924,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920026</v>
+        <v>24330051920233</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D15" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -7941,22 +7947,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920026</v>
+        <v>24330051920233</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D16" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -7964,22 +7970,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>24330051920324</v>
+        <v>24330051920326</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D17" t="s">
         <v>104</v>
       </c>
       <c r="E17" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -7987,22 +7993,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>24330051920353</v>
+        <v>24330051920326</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D18" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -8010,22 +8016,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>24330051920141</v>
+        <v>24330051920326</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D19" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F19" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -8033,19 +8039,19 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>24330051920140</v>
+        <v>24330051920307</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D20" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E20" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F20" t="s">
         <v>67</v>
@@ -8056,22 +8062,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>24330051920325</v>
+        <v>24330051920307</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="D21" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E21" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F21" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -8079,24 +8085,162 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>24330051920137</v>
+        <v>24330051920307</v>
       </c>
       <c r="B22" t="s">
+        <v>83</v>
+      </c>
+      <c r="C22" t="s">
+        <v>94</v>
+      </c>
+      <c r="D22" t="s">
+        <v>105</v>
+      </c>
+      <c r="E22" t="s">
+        <v>10</v>
+      </c>
+      <c r="F22" t="s">
+        <v>69</v>
+      </c>
+      <c r="G22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>24330051920103</v>
+      </c>
+      <c r="B23" t="s">
+        <v>84</v>
+      </c>
+      <c r="C23" t="s">
+        <v>95</v>
+      </c>
+      <c r="D23" t="s">
+        <v>106</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>66</v>
+      </c>
+      <c r="G23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>24330051920324</v>
+      </c>
+      <c r="B24" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" t="s">
+        <v>107</v>
+      </c>
+      <c r="E24" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" t="s">
+        <v>68</v>
+      </c>
+      <c r="G24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>24330051920353</v>
+      </c>
+      <c r="B25" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" t="s">
+        <v>97</v>
+      </c>
+      <c r="D25" t="s">
+        <v>108</v>
+      </c>
+      <c r="E25" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25" t="s">
+        <v>67</v>
+      </c>
+      <c r="G25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>24330051920141</v>
+      </c>
+      <c r="B26" t="s">
+        <v>87</v>
+      </c>
+      <c r="C26" t="s">
+        <v>98</v>
+      </c>
+      <c r="D26" t="s">
+        <v>109</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>66</v>
+      </c>
+      <c r="G26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>24330051920026</v>
+      </c>
+      <c r="B27" t="s">
         <v>88</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C27" t="s">
         <v>99</v>
       </c>
-      <c r="D22" t="s">
-        <v>109</v>
-      </c>
-      <c r="E22" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" t="s">
-        <v>67</v>
-      </c>
-      <c r="G22">
+      <c r="D27" t="s">
+        <v>110</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
+        <v>66</v>
+      </c>
+      <c r="G27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>24330051920325</v>
+      </c>
+      <c r="B28" t="s">
+        <v>89</v>
+      </c>
+      <c r="C28" t="s">
+        <v>100</v>
+      </c>
+      <c r="D28" t="s">
+        <v>111</v>
+      </c>
+      <c r="E28" t="s">
+        <v>11</v>
+      </c>
+      <c r="F28" t="s">
+        <v>68</v>
+      </c>
+      <c r="G28">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1AM - Estadisticos 20241.xlsx
+++ b/grupos/1AM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="110">
   <si>
     <t>Materia</t>
   </si>
@@ -254,51 +254,48 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
     <t>CID</t>
   </si>
   <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>RAZCON</t>
+  </si>
+  <si>
+    <t>ESCOBAR</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>RAZCON</t>
-  </si>
-  <si>
-    <t>ESCOBAR</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
+    <t>PAZ</t>
   </si>
   <si>
     <t>OROZCO</t>
   </si>
   <si>
-    <t>RANGEL</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
     <t>ROMERO</t>
   </si>
   <si>
@@ -323,13 +320,10 @@
     <t>MUÑOZ</t>
   </si>
   <si>
+    <t>YERIEL</t>
+  </si>
+  <si>
     <t>ANGEL ALEXANDER</t>
-  </si>
-  <si>
-    <t>AXEL BENITO</t>
-  </si>
-  <si>
-    <t>YERIEL</t>
   </si>
   <si>
     <t>SANTIAGO</t>
@@ -913,7 +907,7 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U4">
         <v>-1</v>
@@ -1002,7 +996,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U5">
         <v>-1</v>
@@ -1023,7 +1017,7 @@
         <v>5</v>
       </c>
       <c r="AA5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB5">
         <v>7</v>
@@ -1091,7 +1085,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U6">
         <v>-1</v>
@@ -1180,7 +1174,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U7">
         <v>-1</v>
@@ -1201,7 +1195,7 @@
         <v>9</v>
       </c>
       <c r="AA7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB7">
         <v>8</v>
@@ -1269,7 +1263,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U8">
         <v>-1</v>
@@ -1290,7 +1284,7 @@
         <v>7</v>
       </c>
       <c r="AA8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB8">
         <v>10</v>
@@ -1358,7 +1352,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U9">
         <v>-1</v>
@@ -1447,7 +1441,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U10">
         <v>-1</v>
@@ -1468,7 +1462,7 @@
         <v>5</v>
       </c>
       <c r="AA10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB10">
         <v>5</v>
@@ -1536,7 +1530,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U11">
         <v>-1</v>
@@ -1557,7 +1551,7 @@
         <v>5</v>
       </c>
       <c r="AA11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB11">
         <v>5</v>
@@ -1625,7 +1619,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U12">
         <v>-1</v>
@@ -1714,7 +1708,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U13">
         <v>-1</v>
@@ -1803,7 +1797,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U14">
         <v>-1</v>
@@ -1824,7 +1818,7 @@
         <v>10</v>
       </c>
       <c r="AA14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB14">
         <v>8</v>
@@ -1892,7 +1886,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U15">
         <v>-1</v>
@@ -1981,7 +1975,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U16">
         <v>-1</v>
@@ -2070,7 +2064,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U17">
         <v>-1</v>
@@ -2091,7 +2085,7 @@
         <v>7</v>
       </c>
       <c r="AA17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB17">
         <v>8</v>
@@ -2159,7 +2153,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U18">
         <v>-1</v>
@@ -2248,7 +2242,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U19">
         <v>-1</v>
@@ -2269,7 +2263,7 @@
         <v>5</v>
       </c>
       <c r="AA19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB19">
         <v>5</v>
@@ -2337,7 +2331,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U20">
         <v>-1</v>
@@ -2358,7 +2352,7 @@
         <v>9</v>
       </c>
       <c r="AA20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB20">
         <v>9</v>
@@ -2426,7 +2420,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U21">
         <v>-1</v>
@@ -2447,7 +2441,7 @@
         <v>5</v>
       </c>
       <c r="AA21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB21">
         <v>8</v>
@@ -2515,7 +2509,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U22">
         <v>-1</v>
@@ -2604,7 +2598,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U23">
         <v>-1</v>
@@ -2625,7 +2619,7 @@
         <v>9</v>
       </c>
       <c r="AA23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB23">
         <v>9</v>
@@ -2693,7 +2687,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U24">
         <v>-1</v>
@@ -2782,7 +2776,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U25">
         <v>-1</v>
@@ -2871,7 +2865,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U26">
         <v>-1</v>
@@ -2892,7 +2886,7 @@
         <v>7</v>
       </c>
       <c r="AA26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB26">
         <v>8</v>
@@ -2960,7 +2954,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U27">
         <v>-1</v>
@@ -3049,7 +3043,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U28">
         <v>-1</v>
@@ -3070,7 +3064,7 @@
         <v>7</v>
       </c>
       <c r="AA28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB28">
         <v>9</v>
@@ -3138,7 +3132,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U29">
         <v>-1</v>
@@ -3227,7 +3221,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U30">
         <v>-1</v>
@@ -3248,7 +3242,7 @@
         <v>5</v>
       </c>
       <c r="AA30">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB30">
         <v>5</v>
@@ -3316,7 +3310,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U31">
         <v>-1</v>
@@ -3337,7 +3331,7 @@
         <v>7</v>
       </c>
       <c r="AA31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB31">
         <v>6</v>
@@ -3405,7 +3399,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U32">
         <v>-1</v>
@@ -3426,7 +3420,7 @@
         <v>10</v>
       </c>
       <c r="AA32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB32">
         <v>8</v>
@@ -3494,7 +3488,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U33">
         <v>-1</v>
@@ -3583,7 +3577,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U34">
         <v>-1</v>
@@ -3672,7 +3666,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U35">
         <v>-1</v>
@@ -3761,7 +3755,7 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U36">
         <v>-1</v>
@@ -3850,7 +3844,7 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U37">
         <v>-1</v>
@@ -3939,7 +3933,7 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U38">
         <v>-1</v>
@@ -4028,7 +4022,7 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U39">
         <v>-1</v>
@@ -4117,7 +4111,7 @@
         <v>-1</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U40">
         <v>-1</v>
@@ -4206,7 +4200,7 @@
         <v>-1</v>
       </c>
       <c r="T41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U41">
         <v>-1</v>
@@ -4227,7 +4221,7 @@
         <v>6</v>
       </c>
       <c r="AA41">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB41">
         <v>8</v>
@@ -4295,7 +4289,7 @@
         <v>-1</v>
       </c>
       <c r="T42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U42">
         <v>-1</v>
@@ -4384,7 +4378,7 @@
         <v>-1</v>
       </c>
       <c r="T43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U43">
         <v>-1</v>
@@ -5003,7 +4997,7 @@
         <v>100</v>
       </c>
       <c r="T10">
-        <v>100</v>
+        <v>62.5</v>
       </c>
       <c r="U10">
         <v>100</v>
@@ -5071,7 +5065,7 @@
         <v>100</v>
       </c>
       <c r="T11">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
       <c r="U11">
         <v>100</v>
@@ -5547,7 +5541,7 @@
         <v>100</v>
       </c>
       <c r="T18">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="U18">
         <v>100</v>
@@ -5615,7 +5609,7 @@
         <v>100</v>
       </c>
       <c r="T19">
-        <v>85</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="U19">
         <v>100</v>
@@ -5955,7 +5949,7 @@
         <v>100</v>
       </c>
       <c r="T24">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
       <c r="U24">
         <v>100</v>
@@ -6159,7 +6153,7 @@
         <v>100</v>
       </c>
       <c r="T27">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="U27">
         <v>100</v>
@@ -6363,7 +6357,7 @@
         <v>100</v>
       </c>
       <c r="T30">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="U30">
         <v>100</v>
@@ -7479,19 +7473,19 @@
         <v>40</v>
       </c>
       <c r="D7">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="2">
-        <v>97.5</v>
+        <v>95</v>
       </c>
       <c r="G7" s="2">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="H7">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7593,7 +7587,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7625,16 +7619,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920328</v>
+        <v>24330051920145</v>
       </c>
       <c r="B2" t="s">
         <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -7648,22 +7642,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920328</v>
+        <v>24330051920145</v>
       </c>
       <c r="B3" t="s">
         <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7671,22 +7665,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920328</v>
+        <v>24330051920145</v>
       </c>
       <c r="B4" t="s">
         <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7694,22 +7688,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920328</v>
+        <v>24330051920145</v>
       </c>
       <c r="B5" t="s">
         <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7717,16 +7711,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920329</v>
+        <v>24330051920233</v>
       </c>
       <c r="B6" t="s">
         <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -7740,16 +7734,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920329</v>
+        <v>24330051920233</v>
       </c>
       <c r="B7" t="s">
         <v>79</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -7763,22 +7757,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920329</v>
+        <v>24330051920233</v>
       </c>
       <c r="B8" t="s">
         <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7786,22 +7780,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920329</v>
+        <v>24330051920328</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
         <v>91</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7809,22 +7803,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920145</v>
+        <v>24330051920328</v>
       </c>
       <c r="B10" t="s">
         <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7832,22 +7826,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920145</v>
+        <v>24330051920328</v>
       </c>
       <c r="B11" t="s">
         <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="D11" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -7855,22 +7849,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>24330051920145</v>
+        <v>24330051920326</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -7878,22 +7872,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920145</v>
+        <v>24330051920326</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C13" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -7901,7 +7895,7 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920233</v>
+        <v>24330051920326</v>
       </c>
       <c r="B14" t="s">
         <v>81</v>
@@ -7910,13 +7904,13 @@
         <v>92</v>
       </c>
       <c r="D14" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -7924,22 +7918,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920233</v>
+        <v>24330051920307</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C15" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D15" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -7947,22 +7941,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920233</v>
+        <v>24330051920307</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D16" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E16" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -7970,7 +7964,7 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>24330051920326</v>
+        <v>24330051920307</v>
       </c>
       <c r="B17" t="s">
         <v>82</v>
@@ -7979,13 +7973,13 @@
         <v>93</v>
       </c>
       <c r="D17" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E17" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -7993,13 +7987,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>24330051920326</v>
+        <v>24330051920103</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D18" t="s">
         <v>104</v>
@@ -8016,16 +8010,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>24330051920326</v>
+        <v>24330051920324</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D19" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E19" t="s">
         <v>11</v>
@@ -8039,16 +8033,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>24330051920307</v>
+        <v>24330051920353</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C20" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D20" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E20" t="s">
         <v>6</v>
@@ -8062,16 +8056,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>24330051920307</v>
+        <v>24330051920141</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -8085,22 +8079,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>24330051920307</v>
+        <v>24330051920026</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C22" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D22" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="E22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -8108,139 +8102,24 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>24330051920103</v>
+        <v>24330051920325</v>
       </c>
       <c r="B23" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D23" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E23" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F23" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>24330051920324</v>
-      </c>
-      <c r="B24" t="s">
-        <v>85</v>
-      </c>
-      <c r="C24" t="s">
-        <v>96</v>
-      </c>
-      <c r="D24" t="s">
-        <v>107</v>
-      </c>
-      <c r="E24" t="s">
-        <v>11</v>
-      </c>
-      <c r="F24" t="s">
-        <v>68</v>
-      </c>
-      <c r="G24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>24330051920353</v>
-      </c>
-      <c r="B25" t="s">
-        <v>86</v>
-      </c>
-      <c r="C25" t="s">
-        <v>97</v>
-      </c>
-      <c r="D25" t="s">
-        <v>108</v>
-      </c>
-      <c r="E25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" t="s">
-        <v>67</v>
-      </c>
-      <c r="G25">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>24330051920141</v>
-      </c>
-      <c r="B26" t="s">
-        <v>87</v>
-      </c>
-      <c r="C26" t="s">
-        <v>98</v>
-      </c>
-      <c r="D26" t="s">
-        <v>109</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>66</v>
-      </c>
-      <c r="G26">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>24330051920026</v>
-      </c>
-      <c r="B27" t="s">
-        <v>88</v>
-      </c>
-      <c r="C27" t="s">
-        <v>99</v>
-      </c>
-      <c r="D27" t="s">
-        <v>110</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>66</v>
-      </c>
-      <c r="G27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>24330051920325</v>
-      </c>
-      <c r="B28" t="s">
-        <v>89</v>
-      </c>
-      <c r="C28" t="s">
-        <v>100</v>
-      </c>
-      <c r="D28" t="s">
-        <v>111</v>
-      </c>
-      <c r="E28" t="s">
-        <v>11</v>
-      </c>
-      <c r="F28" t="s">
-        <v>68</v>
-      </c>
-      <c r="G28">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1AM - Estadisticos 20241.xlsx
+++ b/grupos/1AM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="95">
   <si>
     <t>Materia</t>
   </si>
@@ -218,24 +218,24 @@
     <t>Recursos socioemocionales I</t>
   </si>
   <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
-  </si>
-  <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
     <t>Pesce Bautista Victor Manuel</t>
   </si>
   <si>
@@ -257,37 +257,22 @@
     <t>HUERTA</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>ARELLANO</t>
   </si>
   <si>
     <t>CID</t>
   </si>
   <si>
-    <t>MACHORRO</t>
+    <t>GARCIA</t>
   </si>
   <si>
     <t>RAZCON</t>
   </si>
   <si>
-    <t>ESCOBAR</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
+    <t>RANGEL</t>
   </si>
   <si>
     <t>PAZ</t>
@@ -296,58 +281,28 @@
     <t>OROZCO</t>
   </si>
   <si>
-    <t>ROMERO</t>
+    <t>SANCHEZ</t>
   </si>
   <si>
     <t>ROJAS</t>
   </si>
   <si>
-    <t>JUAN</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
+    <t>YERIEL</t>
+  </si>
+  <si>
+    <t>AXEL BENITO</t>
   </si>
   <si>
     <t>ADRIAN</t>
   </si>
   <si>
-    <t>CALIHUA</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>YERIEL</t>
-  </si>
-  <si>
     <t>ANGEL ALEXANDER</t>
   </si>
   <si>
-    <t>SANTIAGO</t>
+    <t>JOY JARA</t>
   </si>
   <si>
     <t>JOSE ARTURO</t>
-  </si>
-  <si>
-    <t>GIOVANNI ARIEL</t>
-  </si>
-  <si>
-    <t>ANGEL MOISES</t>
-  </si>
-  <si>
-    <t>JOY JARA</t>
-  </si>
-  <si>
-    <t>JOHANAN</t>
-  </si>
-  <si>
-    <t>JESUS ANTONIO</t>
-  </si>
-  <si>
-    <t>IAN</t>
   </si>
 </sst>
 </file>
@@ -898,22 +853,22 @@
         <v>7</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W4">
         <v>8</v>
@@ -987,28 +942,28 @@
         <v>6</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R5">
         <v>6</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
         <v>5</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W5">
         <v>6</v>
       </c>
       <c r="X5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y5">
         <v>6</v>
@@ -1023,7 +978,7 @@
         <v>7</v>
       </c>
       <c r="AC5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1076,22 +1031,22 @@
         <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
         <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>10</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W6">
         <v>10</v>
@@ -1165,28 +1120,28 @@
         <v>7</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>10</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>8</v>
       </c>
       <c r="X7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y7">
         <v>9</v>
@@ -1198,10 +1153,10 @@
         <v>7</v>
       </c>
       <c r="AB7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC7">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:29">
@@ -1254,22 +1209,22 @@
         <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
         <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>10</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -1281,7 +1236,7 @@
         <v>9</v>
       </c>
       <c r="Z8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA8">
         <v>8</v>
@@ -1343,22 +1298,22 @@
         <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>10</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W9">
         <v>10</v>
@@ -1376,7 +1331,7 @@
         <v>9</v>
       </c>
       <c r="AB9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC9">
         <v>10</v>
@@ -1432,28 +1387,28 @@
         <v>5</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R10">
         <v>5</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T10">
         <v>5</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W10">
         <v>5</v>
       </c>
       <c r="X10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y10">
         <v>5</v>
@@ -1521,34 +1476,34 @@
         <v>6</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
         <v>5</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
         <v>7</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W11">
         <v>7</v>
       </c>
       <c r="X11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y11">
         <v>6</v>
       </c>
       <c r="Z11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA11">
         <v>6</v>
@@ -1610,22 +1565,22 @@
         <v>5</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R12">
         <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>7</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>7</v>
@@ -1637,7 +1592,7 @@
         <v>10</v>
       </c>
       <c r="Z12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA12">
         <v>8</v>
@@ -1699,22 +1654,22 @@
         <v>7</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
         <v>10</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W13">
         <v>8</v>
@@ -1788,22 +1743,22 @@
         <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
         <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>10</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W14">
         <v>10</v>
@@ -1821,7 +1776,7 @@
         <v>9</v>
       </c>
       <c r="AB14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC14">
         <v>8</v>
@@ -1877,22 +1832,22 @@
         <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R15">
         <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
         <v>9</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W15">
         <v>8</v>
@@ -1904,16 +1859,16 @@
         <v>8</v>
       </c>
       <c r="Z15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA15">
         <v>8</v>
       </c>
       <c r="AB15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC15">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:29">
@@ -1966,22 +1921,22 @@
         <v>7</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R16">
         <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>6</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W16">
         <v>6</v>
@@ -1993,7 +1948,7 @@
         <v>8</v>
       </c>
       <c r="Z16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA16">
         <v>6</v>
@@ -2055,34 +2010,34 @@
         <v>7</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R17">
         <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
         <v>10</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>7</v>
       </c>
       <c r="X17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>9</v>
       </c>
       <c r="Z17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA17">
         <v>8</v>
@@ -2091,7 +2046,7 @@
         <v>8</v>
       </c>
       <c r="AC17">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2144,43 +2099,43 @@
         <v>6</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
         <v>6</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
         <v>6</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>6</v>
       </c>
       <c r="X18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y18">
         <v>6</v>
       </c>
       <c r="Z18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA18">
         <v>6</v>
       </c>
       <c r="AB18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC18">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:29">
@@ -2233,34 +2188,34 @@
         <v>8</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R19">
         <v>7</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
         <v>5</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W19">
         <v>6</v>
       </c>
       <c r="X19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y19">
         <v>6</v>
       </c>
       <c r="Z19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA19">
         <v>5</v>
@@ -2269,7 +2224,7 @@
         <v>5</v>
       </c>
       <c r="AC19">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2322,22 +2277,22 @@
         <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>10</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W20">
         <v>7</v>
@@ -2411,22 +2366,22 @@
         <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R21">
         <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
         <v>10</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W21">
         <v>7</v>
@@ -2438,7 +2393,7 @@
         <v>9</v>
       </c>
       <c r="Z21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA21">
         <v>8</v>
@@ -2500,22 +2455,22 @@
         <v>7</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
         <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T22">
         <v>10</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W22">
         <v>7</v>
@@ -2527,7 +2482,7 @@
         <v>10</v>
       </c>
       <c r="Z22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA22">
         <v>8</v>
@@ -2589,28 +2544,28 @@
         <v>7</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R23">
         <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>10</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>7</v>
       </c>
       <c r="X23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y23">
         <v>9</v>
@@ -2678,28 +2633,28 @@
         <v>7</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R24">
         <v>5</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T24">
         <v>7</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W24">
         <v>6</v>
       </c>
       <c r="X24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y24">
         <v>5</v>
@@ -2711,7 +2666,7 @@
         <v>6</v>
       </c>
       <c r="AB24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC24">
         <v>5</v>
@@ -2767,34 +2722,34 @@
         <v>7</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R25">
         <v>6</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>7</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W25">
         <v>6</v>
       </c>
       <c r="X25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y25">
         <v>7</v>
       </c>
       <c r="Z25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA25">
         <v>7</v>
@@ -2856,22 +2811,22 @@
         <v>7</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
         <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T26">
         <v>10</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W26">
         <v>6</v>
@@ -2883,7 +2838,7 @@
         <v>9</v>
       </c>
       <c r="Z26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA26">
         <v>8</v>
@@ -2945,34 +2900,34 @@
         <v>7</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
         <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T27">
         <v>7</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W27">
         <v>6</v>
       </c>
       <c r="X27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y27">
         <v>7</v>
       </c>
       <c r="Z27">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA27">
         <v>6</v>
@@ -2981,7 +2936,7 @@
         <v>6</v>
       </c>
       <c r="AC27">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:29">
@@ -3034,28 +2989,28 @@
         <v>8</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R28">
         <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
         <v>10</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W28">
         <v>6</v>
       </c>
       <c r="X28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y28">
         <v>8</v>
@@ -3070,7 +3025,7 @@
         <v>9</v>
       </c>
       <c r="AC28">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:29">
@@ -3123,22 +3078,22 @@
         <v>7</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
         <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
         <v>7</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W29">
         <v>7</v>
@@ -3150,7 +3105,7 @@
         <v>9</v>
       </c>
       <c r="Z29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA29">
         <v>7</v>
@@ -3159,7 +3114,7 @@
         <v>8</v>
       </c>
       <c r="AC29">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3212,34 +3167,34 @@
         <v>8</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R30">
         <v>7</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T30">
         <v>10</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W30">
         <v>6</v>
       </c>
       <c r="X30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y30">
         <v>6</v>
       </c>
       <c r="Z30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA30">
         <v>7</v>
@@ -3301,28 +3256,28 @@
         <v>7</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
         <v>7</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T31">
         <v>5</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W31">
         <v>7</v>
       </c>
       <c r="X31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y31">
         <v>7</v>
@@ -3334,10 +3289,10 @@
         <v>6</v>
       </c>
       <c r="AB31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC31">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3390,28 +3345,28 @@
         <v>10</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R32">
         <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>10</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W32">
         <v>10</v>
       </c>
       <c r="X32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y32">
         <v>10</v>
@@ -3423,7 +3378,7 @@
         <v>8</v>
       </c>
       <c r="AB32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC32">
         <v>10</v>
@@ -3479,22 +3434,22 @@
         <v>9</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R33">
         <v>9</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>9</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W33">
         <v>9</v>
@@ -3512,7 +3467,7 @@
         <v>8</v>
       </c>
       <c r="AB33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC33">
         <v>9</v>
@@ -3568,22 +3523,22 @@
         <v>7</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R34">
         <v>9</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T34">
         <v>8</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W34">
         <v>6</v>
@@ -3657,22 +3612,22 @@
         <v>9</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
         <v>10</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W35">
         <v>9</v>
@@ -3690,7 +3645,7 @@
         <v>8</v>
       </c>
       <c r="AB35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC35">
         <v>9</v>
@@ -3746,28 +3701,28 @@
         <v>7</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R36">
         <v>10</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T36">
         <v>7</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W36">
         <v>8</v>
       </c>
       <c r="X36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y36">
         <v>9</v>
@@ -3835,22 +3790,22 @@
         <v>10</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R37">
         <v>10</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T37">
         <v>8</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W37">
         <v>10</v>
@@ -3924,22 +3879,22 @@
         <v>7</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R38">
         <v>10</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T38">
         <v>8</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W38">
         <v>8</v>
@@ -4013,28 +3968,28 @@
         <v>9</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R39">
         <v>10</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T39">
         <v>8</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W39">
         <v>8</v>
       </c>
       <c r="X39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y39">
         <v>10</v>
@@ -4102,28 +4057,28 @@
         <v>8</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R40">
         <v>10</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T40">
         <v>8</v>
       </c>
       <c r="U40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W40">
         <v>8</v>
       </c>
       <c r="X40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y40">
         <v>9</v>
@@ -4191,28 +4146,28 @@
         <v>6</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R41">
         <v>10</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T41">
         <v>9</v>
       </c>
       <c r="U41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W41">
         <v>6</v>
       </c>
       <c r="X41">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y41">
         <v>9</v>
@@ -4280,28 +4235,28 @@
         <v>7</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R42">
         <v>10</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T42">
         <v>10</v>
       </c>
       <c r="U42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V42">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W42">
         <v>8</v>
       </c>
       <c r="X42">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y42">
         <v>10</v>
@@ -4313,7 +4268,7 @@
         <v>9</v>
       </c>
       <c r="AB42">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC42">
         <v>10</v>
@@ -4369,22 +4324,22 @@
         <v>7</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R43">
         <v>10</v>
       </c>
       <c r="S43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T43">
         <v>10</v>
       </c>
       <c r="U43">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V43">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W43">
         <v>8</v>
@@ -4402,7 +4357,7 @@
         <v>8</v>
       </c>
       <c r="AB43">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC43">
         <v>10</v>
@@ -4663,7 +4618,7 @@
         <v>100</v>
       </c>
       <c r="V5">
-        <v>79.5</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -4784,7 +4739,7 @@
         <v>100</v>
       </c>
       <c r="Q7">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="R7">
         <v>96.90000000000001</v>
@@ -4799,7 +4754,7 @@
         <v>100</v>
       </c>
       <c r="V7">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -4852,7 +4807,7 @@
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R8">
         <v>100</v>
@@ -4867,7 +4822,7 @@
         <v>100</v>
       </c>
       <c r="V8">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -4988,7 +4943,7 @@
         <v>100</v>
       </c>
       <c r="Q10">
-        <v>86.7</v>
+        <v>54.2</v>
       </c>
       <c r="R10">
         <v>59.4</v>
@@ -5000,10 +4955,10 @@
         <v>62.5</v>
       </c>
       <c r="U10">
-        <v>100</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V10">
-        <v>77.3</v>
+        <v>59.4</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -5056,7 +5011,7 @@
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>93.3</v>
+        <v>91.7</v>
       </c>
       <c r="R11">
         <v>96.90000000000001</v>
@@ -5071,7 +5026,7 @@
         <v>100</v>
       </c>
       <c r="V11">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -5139,7 +5094,7 @@
         <v>100</v>
       </c>
       <c r="V12">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -5275,7 +5230,7 @@
         <v>100</v>
       </c>
       <c r="V14">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -5343,7 +5298,7 @@
         <v>100</v>
       </c>
       <c r="V15">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -5411,7 +5366,7 @@
         <v>100</v>
       </c>
       <c r="V16">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -5532,7 +5487,7 @@
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R18">
         <v>98.40000000000001</v>
@@ -5547,7 +5502,7 @@
         <v>100</v>
       </c>
       <c r="V18">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -5600,7 +5555,7 @@
         <v>100</v>
       </c>
       <c r="Q19">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="R19">
         <v>92.2</v>
@@ -5615,7 +5570,7 @@
         <v>100</v>
       </c>
       <c r="V19">
-        <v>84.09999999999999</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -5955,7 +5910,7 @@
         <v>100</v>
       </c>
       <c r="V24">
-        <v>88.59999999999999</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -6023,7 +5978,7 @@
         <v>100</v>
       </c>
       <c r="V25">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -6091,7 +6046,7 @@
         <v>100</v>
       </c>
       <c r="V26">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -6144,7 +6099,7 @@
         <v>100</v>
       </c>
       <c r="Q27">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="R27">
         <v>100</v>
@@ -6159,7 +6114,7 @@
         <v>100</v>
       </c>
       <c r="V27">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -6227,7 +6182,7 @@
         <v>100</v>
       </c>
       <c r="V28">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -6295,7 +6250,7 @@
         <v>100</v>
       </c>
       <c r="V29">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -6348,7 +6303,7 @@
         <v>100</v>
       </c>
       <c r="Q30">
-        <v>90</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="R30">
         <v>85.90000000000001</v>
@@ -6363,7 +6318,7 @@
         <v>100</v>
       </c>
       <c r="V30">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -6431,7 +6386,7 @@
         <v>100</v>
       </c>
       <c r="V31">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -6771,7 +6726,7 @@
         <v>100</v>
       </c>
       <c r="V36">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -6960,7 +6915,7 @@
         <v>100</v>
       </c>
       <c r="Q39">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R39">
         <v>100</v>
@@ -7111,7 +7066,7 @@
         <v>100</v>
       </c>
       <c r="V41">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="42" spans="1:22">
@@ -7179,7 +7134,7 @@
         <v>100</v>
       </c>
       <c r="V42">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:22">
@@ -7304,7 +7259,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
@@ -7313,19 +7268,19 @@
         <v>40</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F2" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G2" s="2">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -7336,7 +7291,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
@@ -7345,19 +7300,19 @@
         <v>40</v>
       </c>
       <c r="D3">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2">
-        <v>82.5</v>
+        <v>92.5</v>
       </c>
       <c r="G3" s="2">
-        <v>17.5</v>
+        <v>7.5</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7368,7 +7323,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
@@ -7377,19 +7332,19 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2">
-        <v>82.5</v>
+        <v>95</v>
       </c>
       <c r="G4" s="2">
-        <v>17.5</v>
+        <v>5</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -7400,7 +7355,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>69</v>
@@ -7409,19 +7364,19 @@
         <v>40</v>
       </c>
       <c r="D5">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G5" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7432,7 +7387,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>70</v>
@@ -7453,7 +7408,7 @@
         <v>5</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>7.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7464,7 +7419,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>71</v>
@@ -7473,19 +7428,19 @@
         <v>40</v>
       </c>
       <c r="D7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="G7" s="2">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="H7">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7587,7 +7542,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7625,16 +7580,16 @@
         <v>78</v>
       </c>
       <c r="C2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D2" t="s">
         <v>89</v>
       </c>
-      <c r="D2" t="s">
-        <v>100</v>
-      </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7648,16 +7603,16 @@
         <v>78</v>
       </c>
       <c r="C3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" t="s">
         <v>89</v>
       </c>
-      <c r="D3" t="s">
-        <v>100</v>
-      </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7671,13 +7626,13 @@
         <v>78</v>
       </c>
       <c r="C4" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" t="s">
         <v>89</v>
       </c>
-      <c r="D4" t="s">
-        <v>100</v>
-      </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
         <v>66</v>
@@ -7694,16 +7649,16 @@
         <v>78</v>
       </c>
       <c r="C5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D5" t="s">
         <v>89</v>
-      </c>
-      <c r="D5" t="s">
-        <v>100</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7711,22 +7666,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920233</v>
+        <v>24330051920329</v>
       </c>
       <c r="B6" t="s">
         <v>79</v>
       </c>
       <c r="C6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" t="s">
         <v>90</v>
       </c>
-      <c r="D6" t="s">
-        <v>97</v>
-      </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7734,19 +7689,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920233</v>
+        <v>24330051920329</v>
       </c>
       <c r="B7" t="s">
         <v>79</v>
       </c>
       <c r="C7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" t="s">
         <v>90</v>
       </c>
-      <c r="D7" t="s">
-        <v>97</v>
-      </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
         <v>66</v>
@@ -7760,19 +7715,19 @@
         <v>24330051920233</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7783,19 +7738,19 @@
         <v>24330051920328</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="D9" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7803,19 +7758,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920328</v>
+        <v>24330051920353</v>
       </c>
       <c r="B10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D10" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
         <v>66</v>
@@ -7826,300 +7781,24 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>24330051920328</v>
+        <v>24330051920307</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>24330051920326</v>
-      </c>
-      <c r="B12" t="s">
-        <v>81</v>
-      </c>
-      <c r="C12" t="s">
-        <v>92</v>
-      </c>
-      <c r="D12" t="s">
-        <v>102</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>67</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>24330051920326</v>
-      </c>
-      <c r="B13" t="s">
-        <v>81</v>
-      </c>
-      <c r="C13" t="s">
-        <v>92</v>
-      </c>
-      <c r="D13" t="s">
-        <v>102</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>66</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>24330051920326</v>
-      </c>
-      <c r="B14" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" t="s">
-        <v>92</v>
-      </c>
-      <c r="D14" t="s">
-        <v>102</v>
-      </c>
-      <c r="E14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" t="s">
-        <v>68</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>24330051920307</v>
-      </c>
-      <c r="B15" t="s">
-        <v>82</v>
-      </c>
-      <c r="C15" t="s">
-        <v>93</v>
-      </c>
-      <c r="D15" t="s">
-        <v>103</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>67</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>24330051920307</v>
-      </c>
-      <c r="B16" t="s">
-        <v>82</v>
-      </c>
-      <c r="C16" t="s">
-        <v>93</v>
-      </c>
-      <c r="D16" t="s">
-        <v>103</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>66</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>24330051920307</v>
-      </c>
-      <c r="B17" t="s">
-        <v>82</v>
-      </c>
-      <c r="C17" t="s">
-        <v>93</v>
-      </c>
-      <c r="D17" t="s">
-        <v>103</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>69</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>24330051920103</v>
-      </c>
-      <c r="B18" t="s">
-        <v>83</v>
-      </c>
-      <c r="C18" t="s">
-        <v>94</v>
-      </c>
-      <c r="D18" t="s">
-        <v>104</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>66</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>24330051920324</v>
-      </c>
-      <c r="B19" t="s">
-        <v>84</v>
-      </c>
-      <c r="C19" t="s">
-        <v>95</v>
-      </c>
-      <c r="D19" t="s">
-        <v>105</v>
-      </c>
-      <c r="E19" t="s">
-        <v>11</v>
-      </c>
-      <c r="F19" t="s">
-        <v>68</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>24330051920353</v>
-      </c>
-      <c r="B20" t="s">
-        <v>85</v>
-      </c>
-      <c r="C20" t="s">
-        <v>96</v>
-      </c>
-      <c r="D20" t="s">
-        <v>106</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>67</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>24330051920141</v>
-      </c>
-      <c r="B21" t="s">
-        <v>86</v>
-      </c>
-      <c r="C21" t="s">
-        <v>97</v>
-      </c>
-      <c r="D21" t="s">
-        <v>107</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>66</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>24330051920026</v>
-      </c>
-      <c r="B22" t="s">
-        <v>87</v>
-      </c>
-      <c r="C22" t="s">
-        <v>98</v>
-      </c>
-      <c r="D22" t="s">
-        <v>108</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>66</v>
-      </c>
-      <c r="G22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>24330051920325</v>
-      </c>
-      <c r="B23" t="s">
-        <v>88</v>
-      </c>
-      <c r="C23" t="s">
-        <v>99</v>
-      </c>
-      <c r="D23" t="s">
-        <v>109</v>
-      </c>
-      <c r="E23" t="s">
-        <v>11</v>
-      </c>
-      <c r="F23" t="s">
-        <v>68</v>
-      </c>
-      <c r="G23">
         <v>5</v>
       </c>
     </row>
